--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_236_R24.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_236_R24.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1147</v>
+        <v>4.8631</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8513</v>
+        <v>4.0701</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2634</v>
+        <v>0.7929</v>
       </c>
       <c r="G2" t="n">
         <v>4.0396</v>
@@ -610,13 +610,13 @@
         <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>4.2349</v>
+        <v>1.9832</v>
       </c>
       <c r="T2" t="n">
-        <v>3.3343</v>
+        <v>1.5531</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9006</v>
+        <v>0.4301</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5024</v>
+        <v>2.6689</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9796</v>
+        <v>3.2469</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4772</v>
+        <v>-0.578</v>
       </c>
       <c r="G3" t="n">
         <v>5.6503</v>
@@ -688,13 +688,13 @@
         <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7385</v>
+        <v>0.905</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3383</v>
+        <v>0.6056</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4002</v>
+        <v>0.2994</v>
       </c>
       <c r="V3" t="n">
         <v>2.1444</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0865</v>
+        <v>2.2029</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2784</v>
+        <v>1.6637</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8081</v>
+        <v>0.5392</v>
       </c>
       <c r="G4" t="n">
         <v>0.9677</v>
@@ -766,13 +766,13 @@
         <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3302</v>
+        <v>1.4466</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4876</v>
+        <v>0.8729</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8426</v>
+        <v>0.5737</v>
       </c>
       <c r="V4" t="n">
         <v>0.2525</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6398</v>
+        <v>1.8075</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5837</v>
+        <v>3.7514</v>
       </c>
       <c r="F5" t="n">
         <v>-1.9439</v>
@@ -844,10 +844,10 @@
         <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5034</v>
+        <v>0.6642</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5975</v>
+        <v>0.5702</v>
       </c>
       <c r="U5" t="n">
         <v>0.094</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. BROWN</t>
+          <t>M. GUDURIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1765</v>
+        <v>-0.6277</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.9055</v>
+        <v>0.5702</v>
       </c>
       <c r="F6" t="n">
-        <v>0.729</v>
+        <v>-1.1979</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7117</v>
+        <v>3.1414</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5377999999999999</v>
+        <v>2.6495</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.174</v>
+        <v>0.4919</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4471</v>
+        <v>3.4449</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4839</v>
+        <v>1.9494</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0368</v>
+        <v>1.4956</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2647</v>
+        <v>-0.3036</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0539</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2108</v>
+        <v>-1.0037</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4639</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>-3.7112</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0009</v>
+        <v>-0.7923</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2987</v>
+        <v>-0.2357</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2978</v>
+        <v>-0.5566</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.4254</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.4975</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. GUDURIC</t>
+          <t>L. BROWN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5267</v>
+        <v>-1.3782</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1417</v>
+        <v>-1.9055</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6684</v>
+        <v>0.5274</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1414</v>
+        <v>-0.7117</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6495</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4919</v>
+        <v>-0.174</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4449</v>
+        <v>-0.4471</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9494</v>
+        <v>-0.4839</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4956</v>
+        <v>0.0368</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3036</v>
+        <v>-0.2647</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7000999999999999</v>
+        <v>-0.0539</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0037</v>
+        <v>-0.2108</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.5515</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.7112</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.6913</v>
+        <v>-0.2025</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6642</v>
+        <v>-0.2987</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0271</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.4254</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.607</v>
+        <v>-1.5563</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1726</v>
+        <v>0.2906</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7797</v>
+        <v>-1.8469</v>
       </c>
       <c r="G8" t="n">
         <v>0.0594</v>
@@ -1078,13 +1078,13 @@
         <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2179</v>
+        <v>-0.1672</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2908</v>
+        <v>-0.1729</v>
       </c>
       <c r="U8" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0057</v>
       </c>
       <c r="V8" t="n">
         <v>-2.1444</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7477</v>
+        <v>-1.9181</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0271</v>
+        <v>-0.5671</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7207</v>
+        <v>-1.351</v>
       </c>
       <c r="G9" t="n">
         <v>-2.6416</v>
@@ -1156,13 +1156,13 @@
         <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0382</v>
+        <v>0.8678</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4208</v>
+        <v>0.8808</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3826</v>
+        <v>-0.013</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. BOOKER</t>
+          <t>L. BOLMARO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1987</v>
+        <v>-3.3104</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1863</v>
+        <v>-3.834</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0125</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8143</v>
+        <v>-3.3805</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4693</v>
+        <v>-1.4598</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3451</v>
+        <v>-1.9206</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.4319</v>
+        <v>-2.8478</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7191</v>
+        <v>-1.6665</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7127</v>
+        <v>-1.1813</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3825</v>
+        <v>-0.5326</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2499</v>
+        <v>0.2067</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6323</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4639</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.3917</v>
+        <v>-2.5515</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5461</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4955</v>
+        <v>-0.0431</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0505</v>
+        <v>-0.5673</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4665</v>
+        <v>1.6083</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1418</v>
+        <v>1.6083</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. BOLMARO</t>
+          <t>D. BOOKER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2265</v>
+        <v>-3.7713</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3805</v>
+        <v>-2.6581</v>
       </c>
       <c r="F11" t="n">
-        <v>0.154</v>
+        <v>-1.1133</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.3805</v>
+        <v>-1.8143</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4598</v>
+        <v>-0.4693</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.9206</v>
+        <v>-1.3451</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.8478</v>
+        <v>-1.4319</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.6665</v>
+        <v>-0.7191</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.1813</v>
+        <v>-0.7127</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5326</v>
+        <v>-0.3825</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2067</v>
+        <v>0.2499</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.6323</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.5515</v>
+        <v>-1.3917</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5266</v>
+        <v>-0.0266</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5895</v>
+        <v>0.0237</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-0.0503</v>
       </c>
       <c r="V11" t="n">
-        <v>1.6083</v>
+        <v>-1.4665</v>
       </c>
       <c r="W11" t="n">
-        <v>1.6083</v>
+        <v>0.1418</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="12">
@@ -1345,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.139699999999999</v>
+        <v>-1.019599999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>3.5079</v>
+        <v>4.628199999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.6479</v>
+        <v>-5.647799999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>7.4382</v>
+        <v>7.438199999999999</v>
       </c>
       <c r="H12" t="n">
         <v>12.9588</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.5209</v>
+        <v>-5.520900000000001</v>
       </c>
       <c r="J12" t="n">
         <v>13.335</v>
@@ -1375,7 +1375,7 @@
         <v>-5.8972</v>
       </c>
       <c r="N12" t="n">
-        <v>2.283</v>
+        <v>2.282999999999999</v>
       </c>
       <c r="O12" t="n">
         <v>-8.180100000000001</v>
@@ -1390,13 +1390,13 @@
         <v>10.4381</v>
       </c>
       <c r="S12" t="n">
-        <v>2.9478</v>
+        <v>4.0678</v>
       </c>
       <c r="T12" t="n">
-        <v>2.635799999999999</v>
+        <v>3.7559</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3119000000000003</v>
+        <v>0.3119</v>
       </c>
       <c r="V12" t="n">
         <v>-3.2477</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.0795</v>
+        <v>5.2983</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7583</v>
+        <v>2.8763</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3212</v>
+        <v>2.422</v>
       </c>
       <c r="G13" t="n">
         <v>1.9707</v>
@@ -1468,13 +1468,13 @@
         <v>3.4793</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3976</v>
+        <v>0.6163</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1221</v>
+        <v>0.2401</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2754</v>
+        <v>0.3763</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5361</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6902</v>
+        <v>2.538</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7524</v>
+        <v>3.3421</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0622</v>
+        <v>-0.8041</v>
       </c>
       <c r="G14" t="n">
         <v>3.2438</v>
@@ -1546,13 +1546,13 @@
         <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8552</v>
+        <v>-1.0073</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8962</v>
+        <v>-0.3064</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.959</v>
+        <v>-0.7009</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3943</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9528</v>
+        <v>0.8177</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8079</v>
+        <v>0.572</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1448</v>
+        <v>0.2457</v>
       </c>
       <c r="G15" t="n">
         <v>-0.6901</v>
@@ -1624,13 +1624,13 @@
         <v>3.0154</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1252</v>
+        <v>-0.2603</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3857</v>
+        <v>0.1498</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5109</v>
+        <v>-0.4101</v>
       </c>
       <c r="V15" t="n">
         <v>1.0722</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8901</v>
+        <v>0.3561</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9324</v>
+        <v>0.1067</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0423</v>
+        <v>0.2494</v>
       </c>
       <c r="G16" t="n">
         <v>-0.9219000000000001</v>
@@ -1702,13 +1702,13 @@
         <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2785</v>
+        <v>-0.2555</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9006</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.622</v>
+        <v>-0.3304</v>
       </c>
       <c r="V16" t="n">
         <v>0.1418</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. BRAZDEIKIS</t>
+          <t>D. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1697</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3398</v>
+        <v>-0.6607</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5095</v>
+        <v>0.5979</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7063</v>
+        <v>-2.5371</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.1212</v>
+        <v>-2.1523</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4149</v>
+        <v>-0.3848</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1271</v>
+        <v>-0.4098</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7527</v>
+        <v>-0.3963</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6257</v>
+        <v>-0.0134</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5792</v>
+        <v>-2.1273</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3684</v>
+        <v>-1.756</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2108</v>
+        <v>-0.3713</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4639</v>
+        <v>2.7834</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6959</v>
+        <v>2.7834</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4635</v>
+        <v>-0.4509</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3734</v>
+        <v>-0.3927</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0901</v>
+        <v>-0.0582</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. BIRUTIS</t>
+          <t>I. BRAZDEIKIS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,37 +1813,37 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2077</v>
+        <v>-0.0689</v>
       </c>
       <c r="E18" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.3398</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.217</v>
+        <v>-0.4087</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1135</v>
+        <v>-0.7063</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9026999999999999</v>
+        <v>-1.1212</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2108</v>
+        <v>0.4149</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7023</v>
+        <v>-0.1271</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7023</v>
+        <v>-0.7527</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.6257</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4112</v>
+        <v>-0.5792</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2004</v>
+        <v>-0.3684</v>
       </c>
       <c r="O18" t="n">
         <v>-0.2108</v>
@@ -1852,34 +1852,34 @@
         <v>0.4639</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4419</v>
+        <v>-0.3626</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7117</v>
+        <v>-0.3734</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2697</v>
+        <v>0.0108</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. ULANOVAS</t>
+          <t>L. BIRUTIS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4151</v>
+        <v>-0.3763</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3387</v>
+        <v>-0.2266</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7538</v>
+        <v>-0.1498</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0733</v>
+        <v>-1.1135</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3745</v>
+        <v>-0.9026999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3012</v>
+        <v>-0.2108</v>
       </c>
       <c r="J19" t="n">
-        <v>0.003</v>
+        <v>-0.7023</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1443</v>
+        <v>-0.7023</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1472</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0762</v>
+        <v>-0.4112</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2303</v>
+        <v>-0.2004</v>
       </c>
       <c r="O19" t="n">
-        <v>0.154</v>
+        <v>-0.2108</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1278</v>
+        <v>0.2732</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2636</v>
+        <v>0.4758</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3914</v>
+        <v>-0.2025</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. GIEDRAITIS</t>
+          <t>E. ULANOVAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9056</v>
+        <v>-0.5438</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6044</v>
+        <v>1.2208</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6987</v>
+        <v>-1.7646</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.5371</v>
+        <v>-1.0733</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.1523</v>
+        <v>-1.3745</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3848</v>
+        <v>0.3012</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4098</v>
+        <v>0.003</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3963</v>
+        <v>-0.1443</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0134</v>
+        <v>0.1472</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1273</v>
+        <v>-1.0762</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.756</v>
+        <v>-1.2303</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3713</v>
+        <v>0.154</v>
       </c>
       <c r="P20" t="n">
-        <v>2.7834</v>
+        <v>0.9278</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7834</v>
+        <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2937</v>
+        <v>-0.2566</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3364</v>
+        <v>0.1456</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0426</v>
+        <v>-0.4022</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1418</v>
+        <v>-0.1418</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9089</v>
+        <v>-1.0268</v>
       </c>
       <c r="E21" t="n">
-        <v>2.6869</v>
+        <v>3.5125</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.5957</v>
+        <v>-4.5393</v>
       </c>
       <c r="G21" t="n">
         <v>1.4341</v>
@@ -2092,13 +2092,13 @@
         <v>2.0876</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4668</v>
+        <v>-0.5847</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1123</v>
+        <v>-0.2867</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3545</v>
+        <v>-0.2981</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2525</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8657</v>
+        <v>-4.0052</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.3736</v>
+        <v>-5.4351</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5079</v>
+        <v>1.4299</v>
       </c>
       <c r="G22" t="n">
         <v>-7.0446</v>
@@ -2170,13 +2170,13 @@
         <v>2.7834</v>
       </c>
       <c r="S22" t="n">
-        <v>1.2665</v>
+        <v>0.127</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0227</v>
+        <v>-0.0389</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2438</v>
+        <v>0.1658</v>
       </c>
       <c r="V22" t="n">
         <v>2.6805</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2.1399</v>
+        <v>2.926299999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>5.6477</v>
+        <v>5.6478</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.507899999999999</v>
+        <v>-2.7216</v>
       </c>
       <c r="G23" t="n">
         <v>-7.438200000000001</v>
@@ -2239,7 +2239,7 @@
         <v>-2.6593</v>
       </c>
       <c r="P23" t="n">
-        <v>9.278099999999998</v>
+        <v>9.2781</v>
       </c>
       <c r="Q23" t="n">
         <v>-10.438</v>
@@ -2248,13 +2248,13 @@
         <v>19.716</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.9477</v>
+        <v>-2.1614</v>
       </c>
       <c r="T23" t="n">
         <v>-0.3119000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.6358</v>
+        <v>-1.8495</v>
       </c>
       <c r="V23" t="n">
         <v>3.2477</v>
